--- a/data/reports/Real_Leads_Aviation.xlsx
+++ b/data/reports/Real_Leads_Aviation.xlsx
@@ -32,7 +32,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEBEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -68,12 +73,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -444,16 +452,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="51" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -496,210 +504,1435 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Civil Aviation, Government of India</t>
+          <t>divya_10_diya</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/MoCAIndia/</t>
+          <t>bookmycollege.cbe</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Hon'ble Civil Aviation Minister Shri Ram Mohan Naidu met Hon'ble CM of Madhya Pradesh Shri Dr Mohan Yadav ji in New Delhi and held detailed discussions on key developmental priorities related to the state.The minister reaffirmed the ministry's commitment to strengthening aviation infrastructure and enhancing regional connectivity across Madhya Pradesh in line with the vision of Hon'ble PM Shri Narendra Modi ji for inclusive growth and improved air connectivity for all.@narendramodi @rammnk @drmohanyadav51 @murlidharkmohol @aaiofficial</t>
+          <t>Fees details</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/MoCAIndia?__cft__[0]=AZYFG97A9ANe3pQw8Pcr3rbaKOs82t2DP5ZBSe85O_1Q8ThsHGbmm5s-h4viCzMgQo8YSJxF93o0V7b8K_uQDgQNLLnXZ6Fv9x9Vv_KmNJQDfMjkc18TqfipP6RKZ9-Z8wOFMF1SdruMkcWGF8uHUZ-hgoyvyc5_wHZF87A8_S9_rg&amp;__tn__=-UC%2CP-R</t>
+          <t>https://instagram.com/divya_10_diya/</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-05-02 07:09:45+00:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Bains Singh Bhupinder</t>
+          <t>divya_10_diya</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/MoCAIndia/</t>
+          <t>bookmycollege.cbe</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Great  very nice</t>
+          <t>Fees details</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/bains.singh.bhupinder?comment_id=Y29tbWVudDoxNDA1NDg2NTUxNjEzNDYyXzEyNzE2Mzg1MTgyODM2Njc%3D&amp;__cft__[0]=AZYFG97A9ANe3pQw8Pcr3rbaKOs82t2DP5ZBSe85O_1Q8ThsHGbmm5s-h4viCzMgQo8YSJxF93o0V7b8K_uQDgQNLLnXZ6Fv9x9Vv_KmNJQDfMjkc18TqfipP6RKZ9-Z8wOFMF1SdruMkcWGF8uHUZ-hgoyvyc5_wHZF87A8_S9_rg&amp;__tn__=R]-R</t>
+          <t>https://instagram.com/divya_10_diya/</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-05-02 07:09:45+00:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Cpgoyal Goyal C P</t>
+          <t>divya_10_diya</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/MoCAIndia/</t>
+          <t>bookmycollege.cbe</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Respected Thanks for calling  As above post coronavirus circumstances n It's pandemic with guidelines thus my photo  on dt 10.04.2020 at home  nisainilyam 153neelkanth nagar idgah hills Prabhu nagar road bhopal india TVC  Chhatrapal ROSHANLAL Goyal +919977232015 vi idea prepaid cpgoyal.gcp34@gmail.com patient care pharmacistRMP NFSG MACP LWO'S B1 CITY PLEASE GLOBALLY  BSNLMOBILE prepaid goyalcp.gcp34@gmail.com +919424364889  mr c p goyal patient care pharmacistRMP NFSG MACP LWO'S B1 CITY PLEASE GLOBALLY</t>
+          <t>Fees details</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/cpgoyal.goyalcp?comment_id=Y29tbWVudDoxNDAyNjY4Mjg4NTYxOTU1XzE5MjE1OTk4Mzg1MzQ1MTE%3D&amp;__cft__[0]=AZbmMiSY3hec_zp9Hma3a7w-T4a4PPlZXE8rwpSuCZjGMe-3q9RPDIfKE4WS6Q1HbXIl26-SpakmTaULs1bYcEt5CCm0pRjdJV9s-eev0sH-O39odxrRxsAIb_0W7AMpIBNIhoz1YE4JqZ1XelOUNRBbsZy15f7E0TNtAMAesDZohw&amp;__tn__=R]-R</t>
+          <t>https://instagram.com/divya_10_diya/</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-05-02 07:09:45+00:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Civil Aviation, Government of India</t>
+          <t>divya_10_diya</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/MoCAIndia/</t>
+          <t>bookmycollege.cbe</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>The 2nd edition of the India Aircraft Leasing &amp; Financing Summit at GIFT City concluded successfully, further strengthening global confidence in India’s rapidly evolving aviation financing ecosystem. The hon'ble minister Shri Ram Mohan Naidu shared the Government’s vision of establishing India as a global hub for aircraft leasing and financing, and assured the industry of continued support under the leadership of Hon’ble Prime Minister Shri Narendra Modi Ji.The Summit provided a constructive roadmap for unlocking the estimated USD 50 billion opportunity for India’s aircraft leasing ecosystem over the coming decade. It was also encouraging to witness Indian carriers collectively indicating aircraft procurement plans worth nearly USD 10–12 billion over the next year.@narendramodi @rammnk @murlidharkmohol</t>
+          <t>Fees details</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/MoCAIndia?__cft__[0]=AZa6tb9T9sfXRWzJZGsccurjIpNvpWf_IWG1y4m62huB2e1pfh4vCVsDrpxQs_8_7Rx23etip_CykyB5dgJ12jSdUGZkDb6OQIlvoaBI9N1aUvajegx-K8BiEn8kCbGBGF40IGa7qDq8lx3Z3N6BViKUDIYckjp67KQqGLtLNC211A&amp;__tn__=-UC%2CP-R</t>
+          <t>https://instagram.com/divya_10_diya/</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-05-02 07:09:45+00:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Md Tarique Anwar</t>
+          <t>divya_10_diya</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/MoCAIndia/</t>
+          <t>bookmycollege.cbe</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Bihar needs direct international flight Ministry of Civil Aviation, Government of India</t>
+          <t>Fees details</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/t.anwer.786?comment_id=Y29tbWVudDoxMzk5NTM0NTc1NTQxOTkzXzEzNTQwNzE5MjY4MjY3MDg%3D&amp;__cft__[0]=AZa6tb9T9sfXRWzJZGsccurjIpNvpWf_IWG1y4m62huB2e1pfh4vCVsDrpxQs_8_7Rx23etip_CykyB5dgJ12jSdUGZkDb6OQIlvoaBI9N1aUvajegx-K8BiEn8kCbGBGF40IGa7qDq8lx3Z3N6BViKUDIYckjp67KQqGLtLNC211A&amp;__tn__=R]-R</t>
+          <t>https://instagram.com/divya_10_diya/</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-05-02 07:09:45+00:00</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Ehtsham Chunnu</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/MoCAIndia/</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>My father was serious in hospital we ara waiting for 20 hour to reache our destinations by 20 hours from Gulf country I fill shame Bihar don't have direct international flights #CMOBihar #samratchoudhary #CivilAviationAuthority #CivilAviationMinister #PMOIndia #NarendraModi #PresidentOfIndia</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/ehtsham.chunnu?comment_id=Y29tbWVudDoxMzk5NTM0NTc1NTQxOTkzXzMzMDYxMDI5MTk1NzI1Nzk%3D&amp;__cft__[0]=AZa6tb9T9sfXRWzJZGsccurjIpNvpWf_IWG1y4m62huB2e1pfh4vCVsDrpxQs_8_7Rx23etip_CykyB5dgJ12jSdUGZkDb6OQIlvoaBI9N1aUvajegx-K8BiEn8kCbGBGF40IGa7qDq8lx3Z3N6BViKUDIYckjp67KQqGLtLNC211A&amp;__tn__=R]-R</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>magic_peach_1841</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>I want to become a pilot near karaikal  place of training but I'm a pure science student</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>https://instagram.com/magic_peach_1841/</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-29 13:44:05+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>thefhoto_stories</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Undoubtedly , Unacademy is The best in coaching. Their experienced educators and mentorship truly stands apart ! Strongly recommended..</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/thefhoto_stories/</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 05:52:47+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>dental_care_professionals</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Recommend this academy to all aspirants.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/dental_care_professionals/</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 04:28:06+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>roshni.karthik</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Known for its best coaching skills and also understanding, handling and taking the students through a smooth path as they travel the journey of pressure</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/roshni.karthik/</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 11:23:30+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>shivaraj0220</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Good in town</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/shivaraj0220/</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 07:07:34+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>rnsathishk</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Excellent and Best coaching centre in Coimbatore</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rnsathishk/</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 08:48:44+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>santhoshdevi3</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Great coaching!!!</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/santhoshdevi3/</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 08:40:30+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>navindazzler</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Really Unacademy doing a great job in Coimbatore. Keep it up</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/navindazzler/</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 06:59:28+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>birur</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Best in town</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/birur/</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 05:41:44+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>birur</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Best in town</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/birur/</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 05:42:05+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>aruna.palanisamy.7</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Best for coachin aspiring children</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/aruna.palanisamy.7/</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 04:40:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>jdinesh.kumar.75</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Best coaching centre  in city,my brother is very much confident now after joining here</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/jdinesh.kumar.75/</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 09:11:34+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>praveen_diav</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Unacademy has knowledgeable faculties and they help us in regional languages also . Good work . Keep it up 👍🏾</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/praveen_diav/</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 12:37:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>kanagarajmounasamy</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Un Academy Is Know one of the Best Centrefor NEET JEE Coaching,.. My Nephew Cleared Medical Exams help of unacademy coaching.. Thanks to Unacademy.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/kanagarajmounasamy/</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 02:43:27+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>praveen_diav</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Unacademy has knowledgeable faculties and they help us in regional languages also . Good work . Keep it up 👍🏾</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/praveen_diav/</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 12:37:09+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>roshni.karthik</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Known for its best coaching skills and also understanding, handling and taking the students through a smooth path as they travel the journey of pressure</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/roshni.karthik/</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 11:23:30+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>thefhoto_stories</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Undoubtedly , Unacademy is The best in coaching. Their experienced educators and mentorship truly stands apart ! Strongly recommended..</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/thefhoto_stories/</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 05:52:47+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>birur</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Best in town</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/birur/</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 05:42:05+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>birur</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Best in town</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/birur/</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 05:41:44+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>aruna.palanisamy.7</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Best for coachin aspiring children</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/aruna.palanisamy.7/</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 04:40:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>dental_care_professionals</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Recommend this academy to all aspirants.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/dental_care_professionals/</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 04:28:06+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>kanagarajmounasamy</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Un Academy Is Know one of the Best Centrefor NEET JEE Coaching,.. My Nephew Cleared Medical Exams help of unacademy coaching.. Thanks to Unacademy.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/kanagarajmounasamy/</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 02:43:27+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>jdinesh.kumar.75</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Best coaching centre  in city,my brother is very much confident now after joining here</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/jdinesh.kumar.75/</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 09:11:34+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>rnsathishk</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Excellent and Best coaching centre in Coimbatore</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rnsathishk/</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 08:48:44+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>santhoshdevi3</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Great coaching!!!</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/santhoshdevi3/</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 08:40:30+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>shivaraj0220</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Good in town</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/shivaraj0220/</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 07:07:34+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>navindazzler</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Really Unacademy doing a great job in Coimbatore. Keep it up</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/navindazzler/</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 06:59:28+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>antobenito72024</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>How much fees</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/antobenito72024/</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-19 05:04:45+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>sri_waves_</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Anna fees evlo agum</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sri_waves_/</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:16:37+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>its_me_blue_queen_001_</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Fees sollunga</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/its_me_blue_queen_001_/</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-25 14:48:44+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>go_ld5744</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Anna fees avlo aagum</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/go_ld5744/</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-01 09:46:44+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>sri_waves_</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Anna fees evlo agum</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sri_waves_/</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:16:37+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>its_me_blue_queen_001_</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Fees sollunga</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/its_me_blue_queen_001_/</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-25 14:48:44+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>antobenito72024</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>How much fees</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/antobenito72024/</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-19 05:04:45+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>go_ld5744</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Anna fees avlo aagum</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/go_ld5744/</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-01 09:46:44+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>sanjudanger10</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>bookmycollege.cbe</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Best advice for life don't consider this college as a college</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sanjudanger10/</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:58:21+00:00</t>
         </is>
       </c>
     </row>
@@ -722,12 +1955,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -752,7 +1985,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -762,7 +1995,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -782,7 +2015,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -802,7 +2035,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -812,7 +2045,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
